--- a/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2993" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2993" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -1216,10 +1216,10 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>取得された結果</t>
-  </si>
-  <si>
-    <t>【JP Core仕様】診断、所見情報記載時に使用。text記載は必須とし、必要に応じてcodingも使用する。</t>
+    <t>【JP Core仕様】診断、所見情報記載時に使用。text記載は必須とし、必要に応じてcodingも使用する</t>
+  </si>
+  <si>
+    <t>【診断、所見情報記載時に使用。text記載は必須とし、必要に応じてcodingも使用する。</t>
   </si>
   <si>
     <t>example</t>
@@ -1234,7 +1234,10 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>【JP Core仕様】診断、所見以外の情報を記載する際、必要に応じて使用。</t>
+    <t>JP Core仕様】診断、所見以外の情報を記載する際、必要に応じて使用</t>
+  </si>
+  <si>
+    <t>診断、所見以外の情報を記載する際、必要に応じて使用する。</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -7921,13 +7924,13 @@
         <v>211</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>376</v>
@@ -8014,10 +8017,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8043,16 +8046,16 @@
         <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8077,13 +8080,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8101,7 +8104,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8110,7 +8113,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8125,7 +8128,7 @@
         <v>137</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8136,14 +8139,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8165,16 +8168,16 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8199,13 +8202,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8223,7 +8226,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8241,27 +8244,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8284,19 +8287,19 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8345,7 +8348,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8366,10 +8369,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8380,10 +8383,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8409,13 +8412,13 @@
         <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8445,7 +8448,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8463,7 +8466,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8481,27 +8484,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8527,16 +8530,16 @@
         <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8564,10 +8567,10 @@
         <v>388</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8585,7 +8588,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8606,10 +8609,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8620,10 +8623,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8646,16 +8649,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8705,7 +8708,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8723,27 +8726,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8766,16 +8769,16 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8825,7 +8828,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8843,27 +8846,27 @@
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8886,19 +8889,19 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8947,7 +8950,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8959,7 +8962,7 @@
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8968,10 +8971,10 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8982,10 +8985,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9100,10 +9103,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9220,14 +9223,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9249,10 +9252,10 @@
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
@@ -9307,7 +9310,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9342,10 +9345,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9368,13 +9371,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9425,7 +9428,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9434,7 +9437,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9446,10 +9449,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9460,10 +9463,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9486,13 +9489,13 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9543,7 +9546,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9552,7 +9555,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9564,10 +9567,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9578,10 +9581,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9607,16 +9610,16 @@
         <v>192</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9644,10 +9647,10 @@
         <v>118</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9665,7 +9668,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9683,13 +9686,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9700,10 +9703,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9729,16 +9732,16 @@
         <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9766,10 +9769,10 @@
         <v>388</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9787,7 +9790,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9805,13 +9808,13 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9822,10 +9825,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9848,17 +9851,17 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9907,7 +9910,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9931,7 +9934,7 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9942,10 +9945,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9971,10 +9974,10 @@
         <v>211</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10025,7 +10028,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10046,10 +10049,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10060,10 +10063,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10086,16 +10089,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10145,7 +10148,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10166,10 +10169,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10180,10 +10183,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10206,16 +10209,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10265,7 +10268,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10286,10 +10289,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10300,10 +10303,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10326,19 +10329,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10387,7 +10390,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10408,10 +10411,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10422,10 +10425,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10540,10 +10543,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10660,14 +10663,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10689,10 +10692,10 @@
         <v>140</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>143</v>
@@ -10747,7 +10750,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10782,10 +10785,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10811,13 +10814,13 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>312</v>
@@ -10848,10 +10851,10 @@
         <v>388</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10869,7 +10872,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>94</v>
@@ -10887,7 +10890,7 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>316</v>
@@ -10904,10 +10907,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10930,16 +10933,16 @@
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>376</v>
@@ -10991,7 +10994,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11009,7 +11012,7 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>381</v>
@@ -11026,10 +11029,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11055,16 +11058,16 @@
         <v>192</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11089,13 +11092,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11113,7 +11116,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11122,7 +11125,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11137,7 +11140,7 @@
         <v>137</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11148,14 +11151,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11177,16 +11180,16 @@
         <v>192</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11211,13 +11214,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11235,7 +11238,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11253,27 +11256,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11299,16 +11302,16 @@
         <v>84</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11357,7 +11360,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11378,10 +11381,10 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -1234,7 +1234,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>JP Core仕様】診断、所見以外の情報を記載する際、必要に応じて使用</t>
+    <t>【JP Core仕様】診断、所見以外の情報を記載する際、必要に応じて使用</t>
   </si>
   <si>
     <t>診断、所見以外の情報を記載する際、必要に応じて使用する。</t>
